--- a/SQExcel.Portal/src/content/docs/ja/docs/images/home-screen/home-screen.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/home-screen/home-screen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\home-screen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\home-screen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB48B3AE-1C52-4BFB-BB36-C1B56DAA36B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6DF686-4704-460E-B0E2-28D47F5EDD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="2808" windowWidth="23040" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="0" windowWidth="19200" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOME-SCREEN" sheetId="3" r:id="rId1"/>
@@ -2354,46 +2354,1772 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>226786</xdr:colOff>
+      <xdr:row>956</xdr:row>
+      <xdr:rowOff>45357</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>219529</xdr:colOff>
+      <xdr:row>991</xdr:row>
+      <xdr:rowOff>199417</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="214" name="グループ化 213">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E4B2EE0-4AB2-E636-89CB-288834FA858F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="458374" y="221443710"/>
+          <a:ext cx="10645802" cy="8259648"/>
+          <a:chOff x="461736" y="218656807"/>
+          <a:chExt cx="10800443" cy="8155060"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="19" name="グループ化 18">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1D68938-A2A3-275B-928E-C163CC75C1F9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="461736" y="218656807"/>
+            <a:ext cx="10800443" cy="8155060"/>
+            <a:chOff x="469900" y="208534000"/>
+            <a:chExt cx="10801350" cy="8155060"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="11" name="図 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17A7D533-B358-22DE-09EF-3E451079D5EC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="208534000"/>
+              <a:ext cx="10801350" cy="8155060"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18" name="正方形/長方形 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2881E43-6AF1-43F4-B88B-7D5B30D5F4FD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="696686" y="216369902"/>
+              <a:ext cx="1635579" cy="237670"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="112" name="正方形/長方形 111">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F4BB23A-C2A0-4072-AB8F-6DB398FA18CB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5258661" y="223977623"/>
+            <a:ext cx="1892808" cy="144713"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="213" name="図 212">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDCED8E8-EA2D-42E6-B927-C678BCC4BBB6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="529666" y="218716038"/>
+            <a:ext cx="252070" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>226786</xdr:colOff>
+      <xdr:row>879</xdr:row>
+      <xdr:rowOff>45356</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>219529</xdr:colOff>
+      <xdr:row>914</xdr:row>
+      <xdr:rowOff>199416</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="209" name="グループ化 208">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D7F8869-C4EF-DEED-DE36-86F4F1987193}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="458374" y="203611415"/>
+          <a:ext cx="10645802" cy="8259648"/>
+          <a:chOff x="461736" y="201054606"/>
+          <a:chExt cx="10800443" cy="8155060"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="169" name="グループ化 168">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60F3F5EA-43B8-6EA2-F0DD-EEDD4FD4AA48}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="461736" y="201054606"/>
+            <a:ext cx="10800443" cy="8155060"/>
+            <a:chOff x="469900" y="191389000"/>
+            <a:chExt cx="10801350" cy="8155060"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="163" name="図 162">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BFA540A-8079-EF7E-6C09-D890E66860EB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="191389000"/>
+              <a:ext cx="10801350" cy="8155060"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="164" name="正方形/長方形 163">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CDB132E-59DF-4505-80F5-DB0C66F178ED}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="732065" y="192833172"/>
+              <a:ext cx="1310821" cy="219529"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="165" name="正方形/長方形 164">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E29D220-33E8-45B4-8D8C-AD6343EFC47B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5232400" y="199188613"/>
+              <a:ext cx="1572986" cy="328386"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="166" name="コネクタ: カギ線 165">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61C69BED-A479-4617-BFC7-DEC5DFE05432}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="164" idx="3"/>
+              <a:endCxn id="165" idx="1"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2042886" y="192942029"/>
+              <a:ext cx="3189514" cy="6409870"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector3">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="110" name="正方形/長方形 109">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{140E3222-C3A6-416A-9878-0B9686E6CAB1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5247989" y="206375423"/>
+            <a:ext cx="1892808" cy="144714"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="208" name="図 207">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74C8B803-A39E-4BAC-B00D-9A132B4E3B2C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="522195" y="201136250"/>
+            <a:ext cx="252070" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9071</xdr:colOff>
+      <xdr:row>820</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>1814</xdr:colOff>
+      <xdr:row>855</xdr:row>
+      <xdr:rowOff>181274</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="207" name="グループ化 206">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97DA1355-B304-9BC6-342F-8A1A8708625F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="240659" y="189929567"/>
+          <a:ext cx="10645802" cy="8259648"/>
+          <a:chOff x="244021" y="187536364"/>
+          <a:chExt cx="10800443" cy="8155060"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="153" name="グループ化 152">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8CE818C-76F2-B867-2D2E-4F515BF5A330}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="244021" y="187536364"/>
+            <a:ext cx="10800443" cy="8155060"/>
+            <a:chOff x="234950" y="167601900"/>
+            <a:chExt cx="10801350" cy="8155060"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="151" name="図 150">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AE0FBF2-8C88-B4A2-4A4A-09AB487D340B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="167601900"/>
+              <a:ext cx="10801350" cy="8155060"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="150" name="図 149">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4226D52-00C9-4A29-DF90-7EFFF206C2A0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1545771" y="169238387"/>
+              <a:ext cx="1897743" cy="1686323"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="152" name="正方形/長方形 151">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A638C888-160D-4DE5-9C72-E4036A7E21C7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1518557" y="170261643"/>
+              <a:ext cx="1934029" cy="330200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="96" name="正方形/長方形 95">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AADBEF31-473C-4FF5-BCF5-EDB34F343646}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5040787" y="192853505"/>
+            <a:ext cx="1892807" cy="144713"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="206" name="図 205">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6B6B8E3-B872-4B2A-9C25-7D5FC49461F2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="294715" y="187583855"/>
+            <a:ext cx="252071" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9071</xdr:colOff>
+      <xdr:row>762</xdr:row>
+      <xdr:rowOff>18143</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>1814</xdr:colOff>
+      <xdr:row>797</xdr:row>
+      <xdr:rowOff>172203</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="205" name="グループ化 204">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D347FCC4-2BC1-4BC2-6ECA-DE81A1BCB78B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="240659" y="176488378"/>
+          <a:ext cx="10645802" cy="8259649"/>
+          <a:chOff x="244021" y="174268493"/>
+          <a:chExt cx="10800443" cy="8155060"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="147" name="グループ化 146">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE5AC0F7-9998-8122-1B31-1BA52696F29A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="244021" y="174268493"/>
+            <a:ext cx="10800443" cy="8155060"/>
+            <a:chOff x="234950" y="153428700"/>
+            <a:chExt cx="10801350" cy="8155060"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="141" name="図 140">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBDA65C9-6D10-7C56-DDA1-3FEBF9C3F930}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="153428700"/>
+              <a:ext cx="10801350" cy="8155060"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="138" name="図 137">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{939A1F53-D415-903A-8262-27D9F33C02C9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1554842" y="155018014"/>
+              <a:ext cx="1892656" cy="1647371"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="140" name="正方形/長方形 139">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7465D5C5-CA81-4EEB-81F1-988BA7F48DB6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1527628" y="155823558"/>
+              <a:ext cx="1924958" cy="246742"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="142" name="正方形/長方形 141">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A5D51D7-0E45-4D67-AABD-8B1F1869E586}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3751036" y="158145843"/>
+              <a:ext cx="6740979" cy="2414814"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="143" name="コネクタ: カギ線 142">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F31A6A1-AB1C-47CF-AABB-99CDB086995D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="144" idx="2"/>
+              <a:endCxn id="142" idx="1"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm rot="16200000" flipH="1">
+              <a:off x="1865072" y="157466379"/>
+              <a:ext cx="3233012" cy="538916"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector2">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="144" name="正方形/長方形 143">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6C5E12E-BD46-4C1B-92BD-6DE586C70F31}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3165953" y="156024943"/>
+              <a:ext cx="92334" cy="94388"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="62" name="正方形/長方形 61">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBDB9B21-F6A4-41CB-AE8A-9697B407A964}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5040787" y="179583795"/>
+            <a:ext cx="1892807" cy="147702"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="204" name="図 203">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D7B0924-7A69-44E0-A973-6A751EEDE56E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="302185" y="174325056"/>
+            <a:ext cx="252071" cy="225938"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>381</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>718</xdr:row>
+      <xdr:rowOff>199572</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>415</xdr:row>
-      <xdr:rowOff>72339</xdr:rowOff>
+      <xdr:row>754</xdr:row>
+      <xdr:rowOff>126846</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="図 27">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="203" name="グループ化 202">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5938A005-754B-FD4D-AD30-82DC10D322C9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE660E17-EB61-2780-6543-39B392A658B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="469900" y="68148200"/>
-          <a:ext cx="10801350" cy="7844740"/>
+          <a:off x="463176" y="166479925"/>
+          <a:ext cx="10650071" cy="8264450"/>
+          <a:chOff x="469900" y="164385172"/>
+          <a:chExt cx="10801350" cy="8156874"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="162" name="グループ化 161">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED590FEF-7436-2B1C-2AEF-A6B08DFD3B60}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="164385172"/>
+            <a:ext cx="10801350" cy="8156874"/>
+            <a:chOff x="469900" y="154771272"/>
+            <a:chExt cx="10801350" cy="8156874"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="155" name="図 154">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{562807AC-5306-CCB2-9FB3-21A6E9A700CD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="154771272"/>
+              <a:ext cx="10801350" cy="8156874"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="156" name="正方形/長方形 155">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CD91ED6-03B2-428D-932F-8074B2B43FB0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="713922" y="155997729"/>
+              <a:ext cx="1383392" cy="255815"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="157" name="正方形/長方形 156">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4C2DA15-0580-472C-B0D8-CB0A4F29F27C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7510236" y="161427885"/>
+              <a:ext cx="1382485" cy="257628"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="158" name="コネクタ: カギ線 157">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA0B881-E04B-45F5-804A-54B43F820690}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="157" idx="2"/>
+              <a:endCxn id="156" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm rot="5400000" flipH="1">
+              <a:off x="2369004" y="155853039"/>
+              <a:ext cx="5560784" cy="6104164"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector4">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -4145"/>
+                <a:gd name="adj2" fmla="val 80088"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="47" name="正方形/長方形 46">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2972A998-3DC9-4C2D-8EEA-69471793DB72}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5266941" y="169703094"/>
+            <a:ext cx="1893619" cy="147755"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="202" name="図 201">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75767612-BFA1-49B3-B1CF-1956FE91AC9A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="507254" y="164444082"/>
+            <a:ext cx="252070" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>655</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>690</xdr:row>
+      <xdr:rowOff>217560</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="201" name="グループ化 200">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8C26AB4-BC4B-4EB7-45D0-B5353E0F7CFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="463176" y="151753794"/>
+          <a:ext cx="10650071" cy="8259648"/>
+          <a:chOff x="469900" y="149840950"/>
+          <a:chExt cx="10801350" cy="8155060"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="94" name="グループ化 93">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F861FECA-7F09-4ADB-C820-D27952CB1560}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="149840950"/>
+            <a:ext cx="10801350" cy="8155060"/>
+            <a:chOff x="469900" y="149840950"/>
+            <a:chExt cx="10801350" cy="8155060"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="92" name="グループ化 91">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C213C48-8BD9-EC47-3576-0A3326B2F2D8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="469900" y="149840950"/>
+              <a:ext cx="10801350" cy="8155060"/>
+              <a:chOff x="469900" y="149777450"/>
+              <a:chExt cx="10801350" cy="8155060"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="87" name="図 86">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31DC9B23-E944-4489-A8E2-6FAF4EF30AD7}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="469900" y="149777450"/>
+                <a:ext cx="10801350" cy="8155060"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="86" name="正方形/長方形 85">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B369196-6A5B-409F-9D35-CB5FA6B8FEAF}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="696686" y="150836994"/>
+                <a:ext cx="1879600" cy="219529"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="93" name="正方形/長方形 92">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C832DF8A-A3C3-44E6-B224-2445ED41CE9A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5187042" y="157631493"/>
+              <a:ext cx="1671711" cy="319314"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="37" name="正方形/長方形 36">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FD2CF2B-D84D-4849-9BD0-D722BB150A39}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5256264" y="155154415"/>
+            <a:ext cx="1893619" cy="144714"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="200" name="図 199">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8DC588E-DFD3-492B-8E58-211EC0D03D47}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="529665" y="149896979"/>
+            <a:ext cx="252070" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -2411,10 +4137,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="14" name="グループ化 13">
+        <xdr:cNvPr id="145" name="グループ化 144">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D878E6DA-B619-27C9-3F4C-F931A06C17D8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BB27683-63D7-935F-E51B-5367D81DEEDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2422,41 +4148,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="507496" y="919153"/>
-          <a:ext cx="11013355" cy="7844061"/>
-          <a:chOff x="436656" y="909917"/>
-          <a:chExt cx="10804712" cy="7841752"/>
+          <a:off x="491701" y="931106"/>
+          <a:ext cx="10650071" cy="7945661"/>
+          <a:chOff x="498425" y="919153"/>
+          <a:chExt cx="10804712" cy="7844061"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="2" name="図 1">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="139" name="グループ化 138">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CA4565B-401E-11D0-7748-9F9E5318D0DB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88B01692-F4F9-9A87-21E8-A6085D97CF23}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="436656" y="909917"/>
-            <a:ext cx="10804712" cy="7841752"/>
+            <a:off x="498425" y="919153"/>
+            <a:ext cx="10804712" cy="7844061"/>
+            <a:chOff x="498425" y="919153"/>
+            <a:chExt cx="10804712" cy="7844061"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="図 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CA4565B-401E-11D0-7748-9F9E5318D0DB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="498425" y="919153"/>
+              <a:ext cx="10804712" cy="7844061"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="129" name="図 128">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{656D2969-079A-497F-9DB4-9DB62DE68296}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="542472" y="977899"/>
+              <a:ext cx="247802" cy="230741"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="3" name="正方形/長方形 2">
@@ -2470,8 +4245,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="477372" y="1472453"/>
-            <a:ext cx="3248584" cy="1914712"/>
+            <a:off x="539298" y="1481059"/>
+            <a:ext cx="3248430" cy="1914728"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2525,8 +4300,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3151468" y="1558365"/>
-            <a:ext cx="470917" cy="266264"/>
+            <a:off x="3213743" y="1566320"/>
+            <a:ext cx="470922" cy="267876"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -2585,8 +4360,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="9668248" y="1535953"/>
-            <a:ext cx="470919" cy="266264"/>
+            <a:off x="9730291" y="1544078"/>
+            <a:ext cx="470924" cy="266062"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -2645,8 +4420,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="9647518" y="3379695"/>
-            <a:ext cx="478015" cy="266264"/>
+            <a:off x="9709481" y="3388373"/>
+            <a:ext cx="478047" cy="266062"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -2705,8 +4480,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3901140" y="1498600"/>
-            <a:ext cx="6738844" cy="1746624"/>
+            <a:off x="3963589" y="1507008"/>
+            <a:ext cx="6738563" cy="1747913"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2760,8 +4535,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3908610" y="3334870"/>
-            <a:ext cx="6738844" cy="1873623"/>
+            <a:off x="3971088" y="3343887"/>
+            <a:ext cx="6738563" cy="1873950"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2815,8 +4590,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3908610" y="5429623"/>
-            <a:ext cx="6738844" cy="2447365"/>
+            <a:off x="3971088" y="5439108"/>
+            <a:ext cx="6738563" cy="2448791"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -2870,8 +4645,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="9662832" y="5474447"/>
-            <a:ext cx="478015" cy="263276"/>
+            <a:off x="9724855" y="5483593"/>
+            <a:ext cx="478047" cy="264910"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -2930,8 +4705,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4068857" y="8431307"/>
-            <a:ext cx="478015" cy="263276"/>
+            <a:off x="4131047" y="8441649"/>
+            <a:ext cx="478046" cy="264911"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -2983,50 +4758,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>73385</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A4C91E5-98DB-2634-F624-81BD9585BDC2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="471714" y="18142857"/>
-          <a:ext cx="8673737" cy="5062671"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
@@ -3039,10 +4770,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="30" name="グループ化 29">
+        <xdr:cNvPr id="159" name="グループ化 158">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1700C9E1-611A-A5F9-11FD-0F67BBF27E82}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2FA87AD-1403-CF5A-2596-A55DB34709BA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3050,41 +4781,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="517071" y="9870621"/>
-          <a:ext cx="11009993" cy="7322672"/>
-          <a:chOff x="508000" y="9848850"/>
-          <a:chExt cx="10801350" cy="7322671"/>
+          <a:off x="501276" y="9977344"/>
+          <a:ext cx="10646709" cy="7418296"/>
+          <a:chOff x="508000" y="9861550"/>
+          <a:chExt cx="10801350" cy="7322672"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="21" name="図 20">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="149" name="グループ化 148">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA1FBCB3-B591-14E0-B64E-709915722DD7}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7DBCFC2-4043-5845-0467-3505E86DCE9C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="508000" y="9848850"/>
-            <a:ext cx="10801350" cy="7314183"/>
+            <a:off x="508000" y="9861550"/>
+            <a:ext cx="10801350" cy="7314251"/>
+            <a:chOff x="508000" y="9861550"/>
+            <a:chExt cx="10801350" cy="7314251"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="図 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA1FBCB3-B591-14E0-B64E-709915722DD7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="508000" y="9861550"/>
+              <a:ext cx="10801350" cy="7314251"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="146" name="図 145">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{785E77CD-CE1F-443B-A85B-399490426639}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="542472" y="9906000"/>
+              <a:ext cx="247802" cy="230742"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="22" name="正方形/長方形 21">
@@ -3098,8 +4878,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7175500" y="16777447"/>
-            <a:ext cx="1204633" cy="394074"/>
+            <a:off x="7175859" y="16789643"/>
+            <a:ext cx="1204751" cy="394579"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3153,8 +4933,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3901140" y="10361706"/>
-            <a:ext cx="7208744" cy="2042459"/>
+            <a:off x="3901549" y="10373969"/>
+            <a:ext cx="7208472" cy="2042595"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3211,8 +4991,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm rot="16200000" flipH="1">
-            <a:off x="5455024" y="14452973"/>
-            <a:ext cx="4373282" cy="275665"/>
+            <a:off x="5455471" y="14465644"/>
+            <a:ext cx="4373080" cy="274915"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector3">
             <a:avLst>
@@ -3259,10 +5039,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="57" name="グループ化 56">
+        <xdr:cNvPr id="179" name="グループ化 178">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E084F19-DE6A-9EFC-B434-85F257BFC2CE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9860964-4AE9-1544-BC2E-D356CDE1E615}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3270,41 +5050,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="478971" y="41877344"/>
-          <a:ext cx="11005458" cy="7118340"/>
-          <a:chOff x="469900" y="40919401"/>
-          <a:chExt cx="10801350" cy="7118341"/>
+          <a:off x="463176" y="42380648"/>
+          <a:ext cx="10650071" cy="7210975"/>
+          <a:chOff x="469900" y="41859201"/>
+          <a:chExt cx="10801350" cy="7118340"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="33" name="図 32">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="178" name="グループ化 177">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0649F2E6-916C-258C-52FD-538A894F6957}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DED1240-2520-C264-36BF-77AD0D9EAD31}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="469900" y="40919401"/>
-            <a:ext cx="10801350" cy="7118341"/>
+            <a:off x="469900" y="41859201"/>
+            <a:ext cx="10801350" cy="7118340"/>
+            <a:chOff x="469900" y="41859201"/>
+            <a:chExt cx="10801350" cy="7118340"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="33" name="図 32">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0649F2E6-916C-258C-52FD-538A894F6957}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="41859201"/>
+              <a:ext cx="10801350" cy="7118340"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="177" name="図 176">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB14C649-DCCB-43FC-81E4-12AF01C8BCB7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="499784" y="41896554"/>
+              <a:ext cx="252070" cy="225939"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="34" name="正方形/長方形 33">
@@ -3318,8 +5147,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6843432" y="44869100"/>
-            <a:ext cx="811039" cy="301171"/>
+            <a:off x="6844934" y="45809499"/>
+            <a:ext cx="809765" cy="302102"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3373,8 +5202,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="559548" y="41717260"/>
-            <a:ext cx="2469028" cy="303306"/>
+            <a:off x="558292" y="42658478"/>
+            <a:ext cx="2468065" cy="304265"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3431,8 +5260,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm rot="10800000">
-            <a:off x="1794063" y="42020567"/>
-            <a:ext cx="5011323" cy="2868515"/>
+            <a:off x="1792325" y="42962744"/>
+            <a:ext cx="5011734" cy="2866997"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -3472,8 +5301,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3795486" y="45417014"/>
-            <a:ext cx="7337878" cy="2196353"/>
+            <a:off x="3795973" y="46358566"/>
+            <a:ext cx="7339322" cy="2195053"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3534,8 +5363,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7654471" y="45018779"/>
-            <a:ext cx="868038" cy="334736"/>
+            <a:off x="7654699" y="45961126"/>
+            <a:ext cx="869329" cy="333115"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -3575,8 +5404,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="8476342" y="45353515"/>
-            <a:ext cx="92334" cy="94388"/>
+            <a:off x="8478507" y="46294241"/>
+            <a:ext cx="91041" cy="95616"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3628,8 +5457,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6805385" y="44841887"/>
-            <a:ext cx="91427" cy="94388"/>
+            <a:off x="6804058" y="45781932"/>
+            <a:ext cx="93509" cy="95616"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3686,10 +5515,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="61" name="グループ化 60">
+        <xdr:cNvPr id="173" name="グループ化 172">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9444482B-B83D-6D1E-0081-1F8DF0EF44F4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{607DE0B9-865E-EB7F-3A28-1DD0DB4E62F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3697,41 +5526,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="488043" y="24527330"/>
-          <a:ext cx="11009086" cy="7118341"/>
+          <a:off x="472248" y="24825300"/>
+          <a:ext cx="10645802" cy="7210976"/>
           <a:chOff x="478972" y="24518259"/>
           <a:chExt cx="10800443" cy="7118341"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="25" name="図 24">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="172" name="グループ化 171">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{566EB8EF-C0A3-D09B-9EE6-4A9A8886AFF0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B64C534B-B1AC-1897-BBA3-A50B9CADABB2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
             <a:off x="478972" y="24518259"/>
             <a:ext cx="10800443" cy="7118341"/>
+            <a:chOff x="478972" y="24518259"/>
+            <a:chExt cx="10800443" cy="7118341"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="25" name="図 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{566EB8EF-C0A3-D09B-9EE6-4A9A8886AFF0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="478972" y="24518259"/>
+              <a:ext cx="10800443" cy="7118341"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="168" name="図 167">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4356F4DE-7CC2-4FC5-B9BF-AA5D70FAE1E6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="537136" y="24547605"/>
+              <a:ext cx="252070" cy="225939"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="60" name="正方形/長方形 59">
@@ -3745,8 +5623,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3940629" y="26904044"/>
-            <a:ext cx="7096862" cy="2012042"/>
+            <a:off x="3938129" y="26905209"/>
+            <a:ext cx="7096102" cy="2011332"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3805,10 +5683,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="64" name="グループ化 63">
+        <xdr:cNvPr id="176" name="グループ化 175">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A201A1F0-C0A6-18A3-064F-87F58BE67053}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2337339F-B137-EF6B-FC2F-6A01CB7347F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3816,41 +5694,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="488043" y="33446358"/>
-          <a:ext cx="11009086" cy="7400335"/>
+          <a:off x="472248" y="33839097"/>
+          <a:ext cx="10645802" cy="7495959"/>
           <a:chOff x="478972" y="33428215"/>
           <a:chExt cx="10800443" cy="7400335"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="31" name="図 30">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="175" name="グループ化 174">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5629ECDC-3A96-E7EC-BF26-11640E4B17A1}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F972E208-9825-D5B5-701A-FBC3278CD12A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
             <a:off x="478972" y="33428215"/>
             <a:ext cx="10800443" cy="7400335"/>
+            <a:chOff x="478972" y="33428215"/>
+            <a:chExt cx="10800443" cy="7400335"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="31" name="図 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5629ECDC-3A96-E7EC-BF26-11640E4B17A1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="478972" y="33428215"/>
+              <a:ext cx="10800443" cy="7400335"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="174" name="図 173">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42A0B54B-A738-4E19-99D1-D172021C97DA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="522195" y="33483177"/>
+              <a:ext cx="252070" cy="225938"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="32" name="正方形/長方形 31">
@@ -3864,8 +5791,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3956499" y="35910032"/>
-            <a:ext cx="7095249" cy="2126602"/>
+            <a:off x="3953772" y="35912218"/>
+            <a:ext cx="7097874" cy="2124199"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3919,8 +5846,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="4030435" y="37515800"/>
-            <a:ext cx="2891972" cy="346529"/>
+            <a:off x="4030011" y="37517818"/>
+            <a:ext cx="2890906" cy="345030"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3979,10 +5906,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="75" name="グループ化 74">
+        <xdr:cNvPr id="182" name="グループ化 181">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F5835AB-AA4C-48F3-3C6F-166334D09212}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFF6878D-3A71-FCC4-B587-7DF9C4D68F8D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3990,41 +5917,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="448128" y="50315587"/>
-          <a:ext cx="11009086" cy="7402149"/>
-          <a:chOff x="469900" y="49403000"/>
-          <a:chExt cx="10801350" cy="7400335"/>
+          <a:off x="440230" y="50926468"/>
+          <a:ext cx="10645802" cy="7500760"/>
+          <a:chOff x="443592" y="50297444"/>
+          <a:chExt cx="10800443" cy="7402149"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="70" name="図 69">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="181" name="グループ化 180">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ED0BE66-96AD-E156-C1EF-972214E58073}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12CABCEF-0D46-7F3E-733A-322277F0FC4C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="469900" y="49403000"/>
-            <a:ext cx="10801350" cy="7400335"/>
+            <a:off x="443592" y="50297444"/>
+            <a:ext cx="10800443" cy="7402149"/>
+            <a:chOff x="443592" y="50297444"/>
+            <a:chExt cx="10800443" cy="7402149"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="70" name="図 69">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ED0BE66-96AD-E156-C1EF-972214E58073}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="443592" y="50297444"/>
+              <a:ext cx="10800443" cy="7402149"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="180" name="図 179">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A81DD88-5264-4F8E-BDDD-EAEFA9B08C70}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="492312" y="50339812"/>
+              <a:ext cx="252070" cy="225939"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
           <xdr:cNvPr id="67" name="図 66">
@@ -4039,15 +6015,15 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1356752" y="50653465"/>
-            <a:ext cx="1986899" cy="1719018"/>
+            <a:off x="1331120" y="51546949"/>
+            <a:ext cx="1988542" cy="1721428"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4067,8 +6043,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1365756" y="50682126"/>
-            <a:ext cx="2005188" cy="310189"/>
+            <a:off x="1339994" y="51575999"/>
+            <a:ext cx="2006568" cy="311410"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4122,8 +6098,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3822701" y="51806928"/>
-            <a:ext cx="7337488" cy="2197142"/>
+            <a:off x="3798536" y="52701124"/>
+            <a:ext cx="7336037" cy="2197076"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4184,8 +6160,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3370944" y="50838128"/>
-            <a:ext cx="451757" cy="2067371"/>
+            <a:off x="3346562" y="51731130"/>
+            <a:ext cx="451974" cy="2068532"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector3">
             <a:avLst/>
@@ -4230,10 +6206,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="88" name="グループ化 87">
+        <xdr:cNvPr id="185" name="グループ化 184">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{647AF374-EFD4-A828-B6C8-AD93BD521E69}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF3DD41D-F87E-500F-3A45-3AD426B742D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4241,41 +6217,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="457202" y="59094913"/>
-          <a:ext cx="11009086" cy="7738720"/>
-          <a:chOff x="199573" y="59085842"/>
+          <a:off x="449304" y="59822335"/>
+          <a:ext cx="10645802" cy="7840320"/>
+          <a:chOff x="452666" y="59076770"/>
           <a:chExt cx="10800443" cy="7738720"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="76" name="図 75">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="184" name="グループ化 183">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C6DD339-797E-05CE-5D04-054C37A112B9}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C07629BE-22F8-C7B8-AD3C-30603FDCAC54}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="199573" y="59085842"/>
+            <a:off x="452666" y="59076770"/>
             <a:ext cx="10800443" cy="7738720"/>
+            <a:chOff x="452666" y="59076770"/>
+            <a:chExt cx="10800443" cy="7738720"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="76" name="図 75">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C6DD339-797E-05CE-5D04-054C37A112B9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="452666" y="59076770"/>
+              <a:ext cx="10800443" cy="7738720"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="183" name="図 182">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD0BC04B-B7B1-404A-8E5A-CBEBAE72F9D8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="484842" y="59123729"/>
+              <a:ext cx="252070" cy="225939"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="79" name="正方形/長方形 78">
@@ -4289,8 +6314,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6608077" y="63182135"/>
-            <a:ext cx="811383" cy="300605"/>
+            <a:off x="6863542" y="63173054"/>
+            <a:ext cx="809851" cy="301564"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4344,8 +6369,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="379366" y="60120512"/>
-            <a:ext cx="2468380" cy="304539"/>
+            <a:off x="633247" y="60113071"/>
+            <a:ext cx="2470017" cy="302561"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4402,8 +6427,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm rot="10800000">
-            <a:off x="1614011" y="60425051"/>
-            <a:ext cx="4956783" cy="2776907"/>
+            <a:off x="1867022" y="60415632"/>
+            <a:ext cx="4959771" cy="2777505"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -4443,8 +6468,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3678334" y="63801920"/>
-            <a:ext cx="7165651" cy="2361452"/>
+            <a:off x="3932044" y="63795000"/>
+            <a:ext cx="7167268" cy="2359584"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4505,8 +6530,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7419460" y="63331531"/>
-            <a:ext cx="1138926" cy="434605"/>
+            <a:off x="7673392" y="63324412"/>
+            <a:ext cx="1139428" cy="434335"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -4546,8 +6571,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="8512044" y="63766136"/>
-            <a:ext cx="92683" cy="95456"/>
+            <a:off x="8767142" y="63758747"/>
+            <a:ext cx="91356" cy="93720"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4599,8 +6624,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6570793" y="63155137"/>
-            <a:ext cx="90866" cy="93642"/>
+            <a:off x="6826792" y="63145702"/>
+            <a:ext cx="89565" cy="94871"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4644,243 +6669,296 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>188846</xdr:colOff>
-      <xdr:row>389</xdr:row>
-      <xdr:rowOff>155047</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>381</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>215494</xdr:colOff>
-      <xdr:row>397</xdr:row>
-      <xdr:rowOff>1150</xdr:rowOff>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>415</xdr:row>
+      <xdr:rowOff>72339</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="194" name="グループ化 193">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF84BEDB-7755-22AC-2551-B15384E23F38}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F03AB5C6-244C-7C9F-AB0C-32A80A1DDFE5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1578375" y="71021047"/>
-          <a:ext cx="1879354" cy="1694007"/>
+          <a:off x="463176" y="88235118"/>
+          <a:ext cx="10650071" cy="7946339"/>
+          <a:chOff x="469900" y="87128350"/>
+          <a:chExt cx="10801350" cy="7844739"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>108379</xdr:colOff>
-      <xdr:row>390</xdr:row>
-      <xdr:rowOff>202648</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>37551</xdr:colOff>
-      <xdr:row>392</xdr:row>
-      <xdr:rowOff>44505</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="正方形/長方形 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05DF73B7-E365-4A14-86EF-9E5D7FFC7960}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1497908" y="71300236"/>
-          <a:ext cx="2013467" cy="305033"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050">
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="193" name="グループ化 192">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F50BA13-66B1-74CF-47A8-0EF3A619E25E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="87128350"/>
+            <a:ext cx="10801350" cy="7844739"/>
+            <a:chOff x="469900" y="87128350"/>
+            <a:chExt cx="10801350" cy="7844739"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="28" name="図 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5938A005-754B-FD4D-AD30-82DC10D322C9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="87128350"/>
+              <a:ext cx="10801350" cy="7844739"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="192" name="図 191">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D92DE4EF-5915-465F-969C-8D41B4D2515F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="514724" y="87188114"/>
+              <a:ext cx="252070" cy="225939"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="12" name="図 11">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF84BEDB-7755-22AC-2551-B15384E23F38}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1598546" y="89112197"/>
+            <a:ext cx="1906248" cy="1674903"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="15" name="正方形/長方形 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05DF73B7-E365-4A14-86EF-9E5D7FFC7960}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1518079" y="89388398"/>
+            <a:ext cx="2043722" cy="299057"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="16" name="コネクタ: カギ線 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E4CECE0-7204-48E8-99AD-9234ACD0D913}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="17" idx="2"/>
+            <a:endCxn id="15" idx="1"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="16200000" flipH="1">
+            <a:off x="757142" y="88776989"/>
+            <a:ext cx="957381" cy="564493"/>
+          </a:xfrm>
+          <a:prstGeom prst="bentConnector2">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="17" name="正方形/長方形 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7604A758-4DC3-4D6B-AF9C-C1E082A1BBB3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="905169" y="88487936"/>
+            <a:ext cx="93472" cy="92611"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
           <a:solidFill>
-            <a:srgbClr val="FF0000"/>
+            <a:srgbClr val="FFC000"/>
           </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-          <a:prstTxWarp prst="textNoShape">
-            <a:avLst/>
-          </a:prstTxWarp>
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>13786</xdr:colOff>
-      <xdr:row>387</xdr:row>
-      <xdr:rowOff>80595</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>108379</xdr:colOff>
-      <xdr:row>391</xdr:row>
-      <xdr:rowOff>123576</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="コネクタ: カギ線 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E4CECE0-7204-48E8-99AD-9234ACD0D913}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="17" idx="2"/>
-          <a:endCxn id="15" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="16200000" flipH="1">
-          <a:off x="734357" y="70689201"/>
-          <a:ext cx="969333" cy="557769"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector2">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>200319</xdr:colOff>
-      <xdr:row>386</xdr:row>
-      <xdr:rowOff>216586</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>58841</xdr:colOff>
-      <xdr:row>387</xdr:row>
-      <xdr:rowOff>80597</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="正方形/長方形 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7604A758-4DC3-4D6B-AF9C-C1E082A1BBB3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="895084" y="70387821"/>
-          <a:ext cx="90110" cy="95599"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFC000"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="0000FF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="0000FF"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -4910,7 +6988,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4954,7 +7032,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4986,10 +7064,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="49" name="グループ化 48">
+        <xdr:cNvPr id="188" name="グループ化 187">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{132B54D3-3960-D7C1-6AC3-72FEA74412AD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C01571E8-B545-FEE5-45EA-ABCD4E1168AD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4997,41 +7075,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="478971" y="68394943"/>
-          <a:ext cx="11005458" cy="7844739"/>
+          <a:off x="463176" y="69244882"/>
+          <a:ext cx="10650071" cy="7946339"/>
           <a:chOff x="469900" y="68376800"/>
           <a:chExt cx="10801350" cy="7844739"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="38" name="図 37">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="187" name="グループ化 186">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1390A69D-A869-8C50-6ED3-0E5A764A616C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BD6D484-5949-8C18-DA71-5E5EDEC6EFD6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
             <a:off x="469900" y="68376800"/>
             <a:ext cx="10801350" cy="7844739"/>
+            <a:chOff x="469900" y="68376800"/>
+            <a:chExt cx="10801350" cy="7844739"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="38" name="図 37">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1390A69D-A869-8C50-6ED3-0E5A764A616C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="68376800"/>
+              <a:ext cx="10801350" cy="7844739"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="186" name="図 185">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EBFBE08-7464-43B2-BE25-1EA111992895}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="507253" y="68414153"/>
+              <a:ext cx="252070" cy="225938"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="41" name="正方形/長方形 40">
@@ -5045,8 +7172,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="529666" y="69395788"/>
-            <a:ext cx="2454087" cy="569259"/>
+            <a:off x="528829" y="69397032"/>
+            <a:ext cx="2453333" cy="570655"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5100,8 +7227,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5236136" y="72772494"/>
-            <a:ext cx="1599826" cy="171823"/>
+            <a:off x="5236617" y="72772647"/>
+            <a:ext cx="1600952" cy="174048"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5158,8 +7285,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2983753" y="69680417"/>
-            <a:ext cx="2252383" cy="3177989"/>
+            <a:off x="2982162" y="69682359"/>
+            <a:ext cx="2254455" cy="3177313"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector3">
             <a:avLst>
@@ -5206,10 +7333,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="65" name="グループ化 64">
+        <xdr:cNvPr id="191" name="グループ化 190">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3A50114-3BC5-9F1A-1CA9-75CA8C8C5A82}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1E0BFD7-0257-A5B1-F87E-747B4F72B13D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5217,41 +7344,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="478971" y="80967944"/>
-          <a:ext cx="11005458" cy="4674291"/>
-          <a:chOff x="469900" y="80492601"/>
+          <a:off x="463176" y="81982236"/>
+          <a:ext cx="10650071" cy="4734056"/>
+          <a:chOff x="469900" y="80949801"/>
           <a:chExt cx="10801350" cy="4674291"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="40" name="図 39">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="190" name="グループ化 189">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CAAEAF9-893F-8C76-8F0C-853E772A77AE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F3439F5-DB36-DE3C-AD7B-B657B96CCE35}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="469900" y="80492601"/>
+            <a:off x="469900" y="80949801"/>
             <a:ext cx="10801350" cy="4674291"/>
+            <a:chOff x="469900" y="80949801"/>
+            <a:chExt cx="10801350" cy="4674291"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="40" name="図 39">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CAAEAF9-893F-8C76-8F0C-853E772A77AE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="80949801"/>
+              <a:ext cx="10801350" cy="4674291"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="189" name="図 188">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FEA497E-799D-4E96-9900-2C116AAAC001}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="499783" y="80994625"/>
+              <a:ext cx="252070" cy="225938"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="51" name="正方形/長方形 50">
@@ -5265,8 +7441,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="542472" y="81497714"/>
-            <a:ext cx="2520949" cy="219529"/>
+            <a:off x="541456" y="81955812"/>
+            <a:ext cx="2522621" cy="219348"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5320,8 +7496,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5187043" y="84469515"/>
-            <a:ext cx="1690007" cy="237671"/>
+            <a:off x="5188212" y="84926763"/>
+            <a:ext cx="1689869" cy="237721"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5378,8 +7554,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm rot="10800000">
-            <a:off x="3063421" y="81606572"/>
-            <a:ext cx="2123622" cy="2980872"/>
+            <a:off x="3064076" y="82066062"/>
+            <a:ext cx="2124135" cy="2980138"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector3">
             <a:avLst>
@@ -5415,126 +7591,6 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>437</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>449</xdr:row>
-      <xdr:rowOff>76110</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="73" name="グループ化 72">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F31F9A0-235C-160A-F3BE-76431DC3EF5A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="478971" y="99952629"/>
-          <a:ext cx="11005458" cy="2819310"/>
-          <a:chOff x="469900" y="99923600"/>
-          <a:chExt cx="10801350" cy="2819311"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="66" name="図 65">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D34D85-0FA6-6BC4-E798-23F9721EDBCE}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="99923600"/>
-            <a:ext cx="10801350" cy="2819311"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="69" name="正方形/長方形 68">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C94F29D2-E67E-4CC6-9E37-17781486BADE}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="596901" y="101184529"/>
-            <a:ext cx="2593520" cy="375557"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:prstDash val="sysDash"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>457</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -5546,10 +7602,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="95" name="グループ化 94">
+        <xdr:cNvPr id="199" name="グループ化 198">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF76BEA7-F997-9FEC-6388-ECD9062F4608}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F83984E2-5358-80E0-03D9-0B4337900E57}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5557,41 +7613,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="478971" y="104546400"/>
-          <a:ext cx="11005458" cy="8155060"/>
-          <a:chOff x="469900" y="103822500"/>
+          <a:off x="463176" y="105835824"/>
+          <a:ext cx="10650071" cy="8259648"/>
+          <a:chOff x="469900" y="104514650"/>
           <a:chExt cx="10801350" cy="8155060"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="89" name="図 88">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="198" name="グループ化 197">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{970F9C70-EF13-E541-9D74-CFAB83D2D51A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCD206AA-2236-8E1F-6F11-F7DE3E13D496}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="469900" y="103822500"/>
+            <a:off x="469900" y="104514650"/>
             <a:ext cx="10801350" cy="8155060"/>
+            <a:chOff x="469900" y="104514650"/>
+            <a:chExt cx="10801350" cy="8155060"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="89" name="図 88">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{970F9C70-EF13-E541-9D74-CFAB83D2D51A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="104514650"/>
+              <a:ext cx="10801350" cy="8155060"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="197" name="図 196">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51AD4E65-A5C5-4E5D-8D0F-74666822D140}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="522195" y="104566943"/>
+              <a:ext cx="252070" cy="225939"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
           <xdr:cNvPr id="77" name="図 76">
@@ -5606,15 +7711,15 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1925013" y="104854047"/>
-            <a:ext cx="1819852" cy="1609441"/>
+            <a:off x="1924803" y="105547475"/>
+            <a:ext cx="1817896" cy="1609164"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5634,8 +7739,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1915930" y="105423178"/>
-            <a:ext cx="1836324" cy="264390"/>
+            <a:off x="1915848" y="106114940"/>
+            <a:ext cx="1834137" cy="264793"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5689,8 +7794,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3822700" y="108476143"/>
-            <a:ext cx="7211785" cy="2496457"/>
+            <a:off x="3822806" y="109168212"/>
+            <a:ext cx="7211633" cy="2495603"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5747,8 +7852,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm rot="16200000" flipH="1">
-            <a:off x="1310222" y="107210984"/>
-            <a:ext cx="4035896" cy="989062"/>
+            <a:off x="1310051" y="107903831"/>
+            <a:ext cx="4036856" cy="988657"/>
           </a:xfrm>
           <a:prstGeom prst="bentConnector2">
             <a:avLst/>
@@ -5804,8 +7909,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="225877" y="114258270"/>
-          <a:ext cx="8808901" cy="3791691"/>
+          <a:off x="225877" y="115673199"/>
+          <a:ext cx="8516695" cy="3842491"/>
           <a:chOff x="225877" y="114220170"/>
           <a:chExt cx="8641080" cy="3791692"/>
         </a:xfrm>
@@ -5824,7 +7929,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -5914,8 +8019,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="257629" y="119020772"/>
-          <a:ext cx="8804365" cy="3850864"/>
+          <a:off x="249731" y="120498454"/>
+          <a:ext cx="8520057" cy="3901664"/>
           <a:chOff x="253093" y="119211272"/>
           <a:chExt cx="8641080" cy="3850865"/>
         </a:xfrm>
@@ -5934,7 +8039,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -6024,8 +8129,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="257629" y="124004614"/>
-          <a:ext cx="8804365" cy="3893980"/>
+          <a:off x="249731" y="125548038"/>
+          <a:ext cx="8520057" cy="3944780"/>
           <a:chOff x="253093" y="123966514"/>
           <a:chExt cx="8641080" cy="3893980"/>
         </a:xfrm>
@@ -6044,7 +8149,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -6134,8 +8239,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="239486" y="139750800"/>
-          <a:ext cx="8804365" cy="3287500"/>
+          <a:off x="231588" y="141500412"/>
+          <a:ext cx="8520057" cy="3329335"/>
           <a:chOff x="234950" y="139712700"/>
           <a:chExt cx="8641080" cy="3287500"/>
         </a:xfrm>
@@ -6154,7 +8259,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -6244,8 +8349,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="234949" y="134493000"/>
-          <a:ext cx="8808901" cy="4254884"/>
+          <a:off x="234949" y="136173882"/>
+          <a:ext cx="8516695" cy="4308673"/>
           <a:chOff x="234949" y="133769100"/>
           <a:chExt cx="8641080" cy="4254884"/>
         </a:xfrm>
@@ -6264,7 +8369,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -6354,8 +8459,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="239486" y="128778001"/>
-          <a:ext cx="8804365" cy="4217275"/>
+          <a:off x="231588" y="130384177"/>
+          <a:ext cx="8520057" cy="4271064"/>
           <a:chOff x="234950" y="128739901"/>
           <a:chExt cx="8641080" cy="4217275"/>
         </a:xfrm>
@@ -6374,7 +8479,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -6464,8 +8569,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="247649" y="145248085"/>
-          <a:ext cx="8805272" cy="3432000"/>
+          <a:off x="239751" y="147069414"/>
+          <a:ext cx="8520964" cy="3476824"/>
           <a:chOff x="243113" y="145209985"/>
           <a:chExt cx="8641987" cy="3431999"/>
         </a:xfrm>
@@ -6503,7 +8608,7 @@
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
           <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
@@ -6858,8 +8963,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="239486" y="159896631"/>
-          <a:ext cx="8804365" cy="3139188"/>
+          <a:off x="231588" y="161898321"/>
+          <a:ext cx="8520057" cy="3178036"/>
           <a:chOff x="234950" y="149789244"/>
           <a:chExt cx="8854501" cy="3216720"/>
         </a:xfrm>
@@ -6878,7 +8983,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -7024,7 +9129,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7068,7 +9173,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7098,105 +9203,159 @@
       <xdr:row>950</xdr:row>
       <xdr:rowOff>137131</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="170" name="図 169">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="212" name="グループ化 211">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D222B93-EF19-9154-C1AF-06496CFF9998}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FFAA214-ECAD-968E-C2AE-51B119C379F9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="469900" y="200761600"/>
-          <a:ext cx="10801350" cy="6766531"/>
+          <a:off x="463176" y="213292765"/>
+          <a:ext cx="10650071" cy="6853190"/>
+          <a:chOff x="469900" y="210610450"/>
+          <a:chExt cx="10801350" cy="6766531"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>9072</xdr:colOff>
-      <xdr:row>948</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>949</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="171" name="正方形/長方形 170">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2756234-2B13-47F7-9C5F-D8BF9AB838F1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="716643" y="205377143"/>
-          <a:ext cx="2712357" cy="299358"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-          <a:prstTxWarp prst="textNoShape">
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="211" name="グループ化 210">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81E737D8-9CE7-EB1E-4A5B-6505BA26815E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="210610450"/>
+            <a:ext cx="10801350" cy="6766531"/>
+            <a:chOff x="469900" y="210610450"/>
+            <a:chExt cx="10801350" cy="6766531"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="170" name="図 169">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D222B93-EF19-9154-C1AF-06496CFF9998}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="210610450"/>
+              <a:ext cx="10801350" cy="6766531"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="210" name="図 209">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B44F01A0-B238-4B87-842A-08BF3BD61FD4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="484842" y="210647803"/>
+              <a:ext cx="252070" cy="225939"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="171" name="正方形/長方形 170">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2756234-2B13-47F7-9C5F-D8BF9AB838F1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="713922" y="216846150"/>
+            <a:ext cx="2702378" cy="301172"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
             <a:avLst/>
-          </a:prstTxWarp>
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -7226,7 +9385,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7258,10 +9417,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="59" name="グループ化 58">
+        <xdr:cNvPr id="218" name="グループ化 217">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EB45261-6C5E-AE94-790D-A7EF3CE726B5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C11D320F-F43D-CEC5-C6BB-E5B4D9197CD3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7269,41 +9428,90 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="471073" y="241831478"/>
-          <a:ext cx="11013355" cy="3918757"/>
-          <a:chOff x="451597" y="230959212"/>
+          <a:off x="463175" y="244848529"/>
+          <a:ext cx="10650071" cy="3969557"/>
+          <a:chOff x="466537" y="241772514"/>
           <a:chExt cx="10804712" cy="3918757"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="58" name="図 57">
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="217" name="グループ化 216">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB1CF002-E20A-2546-323A-795BC8862103}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D073ABFE-AADA-824D-1FF4-09C554DDA65E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="451597" y="230959212"/>
+            <a:off x="466537" y="241772514"/>
             <a:ext cx="10804712" cy="3918757"/>
+            <a:chOff x="466537" y="241772514"/>
+            <a:chExt cx="10804712" cy="3918757"/>
           </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="58" name="図 57">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB1CF002-E20A-2546-323A-795BC8862103}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="466537" y="241772514"/>
+              <a:ext cx="10804712" cy="3918757"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="216" name="図 215">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F386409-B5BA-413B-A892-4AF9656A3D78}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="514724" y="241839749"/>
+              <a:ext cx="252070" cy="225939"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
           <xdr:cNvPr id="48" name="図 47">
@@ -7318,15 +9526,15 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2502123" y="231247484"/>
-            <a:ext cx="2061134" cy="1050001"/>
+            <a:off x="2517971" y="242061535"/>
+            <a:ext cx="2061890" cy="1048671"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7346,8 +9554,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2526853" y="231484420"/>
-            <a:ext cx="1784411" cy="296499"/>
+            <a:off x="2542347" y="242298554"/>
+            <a:ext cx="1785766" cy="297355"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7394,22 +9602,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>655</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:colOff>9071</xdr:colOff>
+      <xdr:row>1013</xdr:row>
+      <xdr:rowOff>72582</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>690</xdr:row>
-      <xdr:rowOff>217560</xdr:rowOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>1814</xdr:colOff>
+      <xdr:row>1048</xdr:row>
+      <xdr:rowOff>226642</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="46" name="グループ化 45">
+        <xdr:cNvPr id="128" name="グループ化 127">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C232FBF-D675-11E1-5D2A-F57E6F27A05B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AEA89E5-156A-62EA-1256-5406437B0271}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7417,18 +9625,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="478971" y="149872700"/>
-          <a:ext cx="11005458" cy="8155060"/>
-          <a:chOff x="472440" y="149849840"/>
-          <a:chExt cx="10858500" cy="8155060"/>
+          <a:off x="472247" y="234671464"/>
+          <a:ext cx="10645802" cy="8259649"/>
+          <a:chOff x="478971" y="231726932"/>
+          <a:chExt cx="10800443" cy="8155060"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="94" name="グループ化 93">
+          <xdr:cNvPr id="126" name="グループ化 125">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F861FECA-7F09-4ADB-C820-D27952CB1560}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44030107-7494-71E5-5BC2-D06825934949}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7436,122 +9644,47 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="472440" y="149849840"/>
-            <a:ext cx="10858500" cy="8155060"/>
-            <a:chOff x="469900" y="149840950"/>
-            <a:chExt cx="10801350" cy="8155060"/>
+            <a:off x="478971" y="231726932"/>
+            <a:ext cx="10800443" cy="8155060"/>
+            <a:chOff x="481511" y="231744181"/>
+            <a:chExt cx="10858860" cy="8155086"/>
           </a:xfrm>
         </xdr:grpSpPr>
-        <xdr:grpSp>
-          <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="92" name="グループ化 91">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="29" name="図 28">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C213C48-8BD9-EC47-3576-0A3326B2F2D8}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E41B17E0-532A-AADD-ED2A-3AD791924A9B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
-            <xdr:cNvGrpSpPr/>
-          </xdr:nvGrpSpPr>
-          <xdr:grpSpPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
             <a:xfrm>
-              <a:off x="469900" y="149840950"/>
-              <a:ext cx="10801350" cy="8155060"/>
-              <a:chOff x="469900" y="149777450"/>
-              <a:chExt cx="10801350" cy="8155060"/>
+              <a:off x="481511" y="231744181"/>
+              <a:ext cx="10858860" cy="8155086"/>
             </a:xfrm>
-          </xdr:grpSpPr>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="87" name="図 86">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31DC9B23-E944-4489-A8E2-6FAF4EF30AD7}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill>
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm>
-                <a:off x="469900" y="149777450"/>
-                <a:ext cx="10801350" cy="8155060"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-          <xdr:sp macro="" textlink="">
-            <xdr:nvSpPr>
-              <xdr:cNvPr id="86" name="正方形/長方形 85">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B369196-6A5B-409F-9D35-CB5FA6B8FEAF}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvSpPr/>
-            </xdr:nvSpPr>
-            <xdr:spPr>
-              <a:xfrm>
-                <a:off x="696686" y="150836994"/>
-                <a:ext cx="1879600" cy="219529"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-              <a:noFill/>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:ln>
-            </xdr:spPr>
-            <xdr:style>
-              <a:lnRef idx="2">
-                <a:schemeClr val="accent1">
-                  <a:shade val="15000"/>
-                </a:schemeClr>
-              </a:lnRef>
-              <a:fillRef idx="1">
-                <a:schemeClr val="accent1"/>
-              </a:fillRef>
-              <a:effectRef idx="0">
-                <a:schemeClr val="accent1"/>
-              </a:effectRef>
-              <a:fontRef idx="minor">
-                <a:schemeClr val="lt1"/>
-              </a:fontRef>
-            </xdr:style>
-            <xdr:txBody>
-              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-                <a:prstTxWarp prst="textNoShape">
-                  <a:avLst/>
-                </a:prstTxWarp>
-                <a:noAutofit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-              </a:p>
-            </xdr:txBody>
-          </xdr:sp>
-        </xdr:grpSp>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="93" name="正方形/長方形 92">
+            <xdr:cNvPr id="125" name="正方形/長方形 124">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C832DF8A-A3C3-44E6-B224-2445ED41CE9A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11A40551-DC25-45F5-B7D7-30A4E26A700E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7559,8 +9692,260 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5187042" y="157631493"/>
-              <a:ext cx="1671711" cy="319314"/>
+              <a:off x="5316584" y="237070174"/>
+              <a:ext cx="1903258" cy="145832"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="127" name="図 126">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85B3776E-2B3D-4712-972A-1596C4C113F7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="506185" y="231781351"/>
+            <a:ext cx="247802" cy="230741"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>73385</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="167" name="グループ化 166">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DDB3432-F551-D363-35CB-6137A5F1512A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="463176" y="18527059"/>
+          <a:ext cx="8520057" cy="5168326"/>
+          <a:chOff x="469900" y="18300700"/>
+          <a:chExt cx="8641080" cy="5102585"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="24" name="図 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A4C91E5-98DB-2634-F624-81BD9585BDC2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="469900" y="18300700"/>
+            <a:ext cx="8641080" cy="5102585"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="161" name="図 160">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC0257EA-CC4D-4F90-8D50-B25DD79AB502}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="492312" y="18330582"/>
+            <a:ext cx="252070" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>437</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>449</xdr:row>
+      <xdr:rowOff>76110</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="196" name="グループ化 195">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E866F10-5BC1-9763-7DD4-06BE8134FBDA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="463176" y="101204059"/>
+          <a:ext cx="10650071" cy="2855169"/>
+          <a:chOff x="469900" y="99929950"/>
+          <a:chExt cx="10801350" cy="2819310"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="73" name="グループ化 72">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F31F9A0-235C-160A-F3BE-76431DC3EF5A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="99929950"/>
+            <a:ext cx="10801350" cy="2819310"/>
+            <a:chOff x="469900" y="99923600"/>
+            <a:chExt cx="10801350" cy="2819311"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="66" name="図 65">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D34D85-0FA6-6BC4-E798-23F9721EDBCE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="99923600"/>
+              <a:ext cx="10801350" cy="2819311"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="69" name="正方形/長方形 68">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C94F29D2-E67E-4CC6-9E37-17781486BADE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="596901" y="101184529"/>
+              <a:ext cx="2593520" cy="375557"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7570,6 +9955,7 @@
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
+              <a:prstDash val="sysDash"/>
             </a:ln>
           </xdr:spPr>
           <xdr:style>
@@ -7602,1429 +9988,12 @@
           </xdr:txBody>
         </xdr:sp>
       </xdr:grpSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="37" name="正方形/長方形 36">
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="195" name="図 194">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FD2CF2B-D84D-4849-9BD0-D722BB150A39}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5283925" y="155163883"/>
-            <a:ext cx="1903258" cy="145832"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>718</xdr:row>
-      <xdr:rowOff>199572</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>754</xdr:row>
-      <xdr:rowOff>126846</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="54" name="グループ化 53">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A62A9AC-D656-3A80-691E-C2B1EDFC5A28}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="478971" y="164421458"/>
-          <a:ext cx="11005458" cy="8156874"/>
-          <a:chOff x="472440" y="164395332"/>
-          <a:chExt cx="10858500" cy="8156874"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="162" name="グループ化 161">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED590FEF-7436-2B1C-2AEF-A6B08DFD3B60}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="472440" y="164395332"/>
-            <a:ext cx="10858500" cy="8156874"/>
-            <a:chOff x="469900" y="154771272"/>
-            <a:chExt cx="10801350" cy="8156874"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="155" name="図 154">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{562807AC-5306-CCB2-9FB3-21A6E9A700CD}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="469900" y="154771272"/>
-              <a:ext cx="10801350" cy="8156874"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="156" name="正方形/長方形 155">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CD91ED6-03B2-428D-932F-8074B2B43FB0}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="713922" y="155997729"/>
-              <a:ext cx="1383392" cy="255815"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="157" name="正方形/長方形 156">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4C2DA15-0580-472C-B0D8-CB0A4F29F27C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7510236" y="161427885"/>
-              <a:ext cx="1382485" cy="257628"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:cxnSp macro="">
-          <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="158" name="コネクタ: カギ線 157">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA0B881-E04B-45F5-804A-54B43F820690}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvCxnSpPr>
-              <a:stCxn id="157" idx="2"/>
-              <a:endCxn id="156" idx="3"/>
-            </xdr:cNvCxnSpPr>
-          </xdr:nvCxnSpPr>
-          <xdr:spPr>
-            <a:xfrm rot="5400000" flipH="1">
-              <a:off x="2369004" y="155853039"/>
-              <a:ext cx="5560784" cy="6104164"/>
-            </a:xfrm>
-            <a:prstGeom prst="bentConnector4">
-              <a:avLst>
-                <a:gd name="adj1" fmla="val -4145"/>
-                <a:gd name="adj2" fmla="val 80088"/>
-              </a:avLst>
-            </a:prstGeom>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:tailEnd type="triangle"/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-        </xdr:cxnSp>
-      </xdr:grpSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="47" name="正方形/長方形 46">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2972A998-3DC9-4C2D-8EEA-69471793DB72}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5294811" y="169714817"/>
-            <a:ext cx="1903258" cy="145832"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>9071</xdr:colOff>
-      <xdr:row>762</xdr:row>
-      <xdr:rowOff>18143</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>1814</xdr:colOff>
-      <xdr:row>797</xdr:row>
-      <xdr:rowOff>172203</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="74" name="グループ化 73">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58AFD268-AE8F-55FA-7E2F-D93F7373F762}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="248557" y="174309314"/>
-          <a:ext cx="11009086" cy="8155060"/>
-          <a:chOff x="245291" y="174279923"/>
-          <a:chExt cx="10858863" cy="8155060"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="147" name="グループ化 146">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE5AC0F7-9998-8122-1B31-1BA52696F29A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="245291" y="174279923"/>
-            <a:ext cx="10858863" cy="8155060"/>
-            <a:chOff x="234950" y="153428700"/>
-            <a:chExt cx="10801350" cy="8155060"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="141" name="図 140">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBDA65C9-6D10-7C56-DDA1-3FEBF9C3F930}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="234950" y="153428700"/>
-              <a:ext cx="10801350" cy="8155060"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="138" name="図 137">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{939A1F53-D415-903A-8262-27D9F33C02C9}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1554842" y="155018014"/>
-              <a:ext cx="1892656" cy="1647371"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="140" name="正方形/長方形 139">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7465D5C5-CA81-4EEB-81F1-988BA7F48DB6}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1527628" y="155823558"/>
-              <a:ext cx="1924958" cy="246742"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="142" name="正方形/長方形 141">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A5D51D7-0E45-4D67-AABD-8B1F1869E586}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3751036" y="158145843"/>
-              <a:ext cx="6740979" cy="2414814"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:cxnSp macro="">
-          <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="143" name="コネクタ: カギ線 142">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F31A6A1-AB1C-47CF-AABB-99CDB086995D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvCxnSpPr>
-              <a:stCxn id="144" idx="2"/>
-              <a:endCxn id="142" idx="1"/>
-            </xdr:cNvCxnSpPr>
-          </xdr:nvCxnSpPr>
-          <xdr:spPr>
-            <a:xfrm rot="16200000" flipH="1">
-              <a:off x="1865072" y="157466379"/>
-              <a:ext cx="3233012" cy="538916"/>
-            </a:xfrm>
-            <a:prstGeom prst="bentConnector2">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:tailEnd type="triangle"/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-        </xdr:cxnSp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="144" name="正方形/長方形 143">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6C5E12E-BD46-4C1B-92BD-6DE586C70F31}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3165953" y="156024943"/>
-              <a:ext cx="92334" cy="94388"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="0000FF"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="62" name="正方形/長方形 61">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBDB9B21-F6A4-41CB-AE8A-9697B407A964}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5069477" y="179595779"/>
-            <a:ext cx="1903257" cy="145832"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>9071</xdr:colOff>
-      <xdr:row>820</xdr:row>
-      <xdr:rowOff>27214</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>1814</xdr:colOff>
-      <xdr:row>855</xdr:row>
-      <xdr:rowOff>181274</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="109" name="グループ化 108">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78BA3537-0B82-31CF-7A6E-8E6FF33CE9DC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="248557" y="187577185"/>
-          <a:ext cx="11009086" cy="8155060"/>
-          <a:chOff x="245291" y="187547794"/>
-          <a:chExt cx="10858863" cy="8155060"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="153" name="グループ化 152">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8CE818C-76F2-B867-2D2E-4F515BF5A330}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="245291" y="187547794"/>
-            <a:ext cx="10858863" cy="8155060"/>
-            <a:chOff x="234950" y="167601900"/>
-            <a:chExt cx="10801350" cy="8155060"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="151" name="図 150">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AE0FBF2-8C88-B4A2-4A4A-09AB487D340B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="234950" y="167601900"/>
-              <a:ext cx="10801350" cy="8155060"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="150" name="図 149">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4226D52-00C9-4A29-DF90-7EFFF206C2A0}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1545771" y="169238387"/>
-              <a:ext cx="1897743" cy="1686323"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="152" name="正方形/長方形 151">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A638C888-160D-4DE5-9C72-E4036A7E21C7}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1518557" y="170261643"/>
-              <a:ext cx="1934029" cy="330200"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="96" name="正方形/長方形 95">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AADBEF31-473C-4FF5-BCF5-EDB34F343646}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5069477" y="192865465"/>
-            <a:ext cx="1903257" cy="145832"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>226786</xdr:colOff>
-      <xdr:row>879</xdr:row>
-      <xdr:rowOff>45356</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>219529</xdr:colOff>
-      <xdr:row>914</xdr:row>
-      <xdr:rowOff>199416</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="111" name="グループ化 110">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0BAE70F-1BA8-2C3B-CB8C-C4AD20AAC9B4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="466272" y="201104499"/>
-          <a:ext cx="11009086" cy="8155060"/>
-          <a:chOff x="463006" y="201068576"/>
-          <a:chExt cx="10858863" cy="8155060"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="169" name="グループ化 168">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60F3F5EA-43B8-6EA2-F0DD-EEDD4FD4AA48}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="463006" y="201068576"/>
-            <a:ext cx="10858863" cy="8155060"/>
-            <a:chOff x="469900" y="191389000"/>
-            <a:chExt cx="10801350" cy="8155060"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="163" name="図 162">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BFA540A-8079-EF7E-6C09-D890E66860EB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="469900" y="191389000"/>
-              <a:ext cx="10801350" cy="8155060"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="164" name="正方形/長方形 163">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CDB132E-59DF-4505-80F5-DB0C66F178ED}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="732065" y="192833172"/>
-              <a:ext cx="1310821" cy="219529"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="165" name="正方形/長方形 164">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E29D220-33E8-45B4-8D8C-AD6343EFC47B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5232400" y="199188613"/>
-              <a:ext cx="1572986" cy="328386"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:cxnSp macro="">
-          <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="166" name="コネクタ: カギ線 165">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61C69BED-A479-4617-BFC7-DEC5DFE05432}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvCxnSpPr>
-              <a:stCxn id="164" idx="3"/>
-              <a:endCxn id="165" idx="1"/>
-            </xdr:cNvCxnSpPr>
-          </xdr:nvCxnSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2042886" y="192942029"/>
-              <a:ext cx="3189514" cy="6409870"/>
-            </a:xfrm>
-            <a:prstGeom prst="bentConnector3">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:tailEnd type="triangle"/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-        </xdr:cxnSp>
-      </xdr:grpSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="110" name="正方形/長方形 109">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{140E3222-C3A6-416A-9878-0B9686E6CAB1}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5273039" y="206389877"/>
-            <a:ext cx="1903258" cy="145832"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>226786</xdr:colOff>
-      <xdr:row>956</xdr:row>
-      <xdr:rowOff>45357</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>219529</xdr:colOff>
-      <xdr:row>991</xdr:row>
-      <xdr:rowOff>199417</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="113" name="グループ化 112">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEF0DA1F-6B17-98D2-4456-358CC084376D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="466272" y="218706700"/>
-          <a:ext cx="11009086" cy="8155060"/>
-          <a:chOff x="463006" y="218670777"/>
-          <a:chExt cx="10858863" cy="8155060"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="19" name="グループ化 18">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1D68938-A2A3-275B-928E-C163CC75C1F9}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="463006" y="218670777"/>
-            <a:ext cx="10858863" cy="8155060"/>
-            <a:chOff x="469900" y="208534000"/>
-            <a:chExt cx="10801350" cy="8155060"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="11" name="図 10">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17A7D533-B358-22DE-09EF-3E451079D5EC}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="469900" y="208534000"/>
-              <a:ext cx="10801350" cy="8155060"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="18" name="正方形/長方形 17">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2881E43-6AF1-43F4-B88B-7D5B30D5F4FD}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="696686" y="216369902"/>
-              <a:ext cx="1635579" cy="237670"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="112" name="正方形/長方形 111">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F4BB23A-C2A0-4072-AB8F-6DB398FA18CB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5283925" y="223992077"/>
-            <a:ext cx="1903258" cy="145832"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>9071</xdr:colOff>
-      <xdr:row>1013</xdr:row>
-      <xdr:rowOff>72571</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>1814</xdr:colOff>
-      <xdr:row>1048</xdr:row>
-      <xdr:rowOff>226631</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="126" name="グループ化 125">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44030107-7494-71E5-5BC2-D06825934949}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="488042" y="231785885"/>
-          <a:ext cx="11009086" cy="8155060"/>
-          <a:chOff x="481511" y="231743431"/>
-          <a:chExt cx="10858863" cy="8155060"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="29" name="図 28">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E41B17E0-532A-AADD-ED2A-3AD791924A9B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83DB466E-A132-439D-B7ED-18F3507B3EE1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9033,67 +10002,21 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="481511" y="231743431"/>
-            <a:ext cx="10858863" cy="8155060"/>
+            <a:off x="514724" y="99982243"/>
+            <a:ext cx="252070" cy="225939"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="125" name="正方形/長方形 124">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11A40551-DC25-45F5-B7D7-30A4E26A700E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5316584" y="237070174"/>
-            <a:ext cx="1903258" cy="145832"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -9128,8 +10051,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="449728" y="962212"/>
-          <a:ext cx="10718801" cy="7328744"/>
+          <a:off x="448234" y="956236"/>
+          <a:ext cx="10650071" cy="7282426"/>
           <a:chOff x="451596" y="944283"/>
           <a:chExt cx="10804712" cy="7189791"/>
         </a:xfrm>
@@ -9723,8 +10646,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="466165" y="46616471"/>
-          <a:ext cx="10717306" cy="5556269"/>
+          <a:off x="463176" y="46317647"/>
+          <a:ext cx="10650071" cy="5521904"/>
           <a:chOff x="469900" y="36804600"/>
           <a:chExt cx="10801350" cy="5453175"/>
         </a:xfrm>
@@ -10190,12 +11113,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247D8D20-CE8B-4D82-A6C6-EA8B8BD03E4C}">
   <dimension ref="A2:CD1057"/>
-  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="16384" width="3.09765625" style="1"/>
+    <col min="1" max="16384" width="3.08203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -10203,18 +11126,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="AN3" s="2"/>
       <c r="CD3" s="2"/>
     </row>
-    <row r="33" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="2"/>
     </row>
-    <row r="40" spans="1:82" s="4" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="41" spans="1:82" s="5" customFormat="1" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:82" s="4" customFormat="1" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="41" spans="1:82" s="5" customFormat="1" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="5" t="s">
         <v>0</v>
       </c>
@@ -10222,24 +11145,24 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="2" t="s">
         <v>19</v>
       </c>
       <c r="AN42" s="2"/>
       <c r="CD42" s="2"/>
     </row>
-    <row r="43" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="2" t="s">
         <v>28</v>
       </c>
       <c r="AN43" s="2"/>
       <c r="CD43" s="2"/>
     </row>
-    <row r="66" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="2"/>
     </row>
-    <row r="78" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1" t="s">
         <v>0</v>
       </c>
@@ -10247,27 +11170,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="2" t="s">
         <v>21</v>
       </c>
       <c r="AN79" s="2"/>
       <c r="CD79" s="2"/>
     </row>
-    <row r="80" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="2" t="s">
         <v>29</v>
       </c>
       <c r="AN80" s="2"/>
       <c r="CD80" s="2"/>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="2"/>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="2"/>
     </row>
-    <row r="105" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="1" t="s">
         <v>0</v>
       </c>
@@ -10275,27 +11198,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="106" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" s="2" t="s">
         <v>22</v>
       </c>
       <c r="AN106" s="2"/>
       <c r="CD106" s="2"/>
     </row>
-    <row r="107" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C107" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" s="2"/>
     </row>
-    <row r="133" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B133" s="2"/>
     </row>
-    <row r="140" spans="1:82" s="4" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="141" spans="1:82" s="5" customFormat="1" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="142" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:82" s="4" customFormat="1" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="141" spans="1:82" s="5" customFormat="1" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="142" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="1" t="s">
         <v>0</v>
       </c>
@@ -10303,14 +11226,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B143" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AN143" s="2"/>
       <c r="CD143" s="2"/>
     </row>
-    <row r="144" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B144" s="2"/>
       <c r="C144" s="1" t="s">
         <v>31</v>
@@ -10318,7 +11241,7 @@
       <c r="AN144" s="2"/>
       <c r="CD144" s="2"/>
     </row>
-    <row r="145" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B145" s="2"/>
       <c r="C145" s="1" t="s">
         <v>32</v>
@@ -10326,16 +11249,16 @@
       <c r="AN145" s="2"/>
       <c r="CD145" s="2"/>
     </row>
-    <row r="151" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B151" s="2"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B170" s="2"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B174" s="2"/>
     </row>
-    <row r="180" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="1" t="s">
         <v>0</v>
       </c>
@@ -10343,14 +11266,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="181" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B181" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AN181" s="2"/>
       <c r="CD181" s="2"/>
     </row>
-    <row r="182" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B182" s="2"/>
       <c r="C182" s="1" t="s">
         <v>33</v>
@@ -10358,18 +11281,18 @@
       <c r="AN182" s="2"/>
       <c r="CD182" s="2"/>
     </row>
-    <row r="183" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C183" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="192" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B192" s="2"/>
     </row>
-    <row r="212" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B212" s="2"/>
     </row>
-    <row r="216" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="1" t="s">
         <v>0</v>
       </c>
@@ -10377,14 +11300,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="217" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B217" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AN217" s="2"/>
       <c r="CD217" s="2"/>
     </row>
-    <row r="218" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B218" s="2"/>
       <c r="C218" s="1" t="s">
         <v>37</v>
@@ -10392,18 +11315,18 @@
       <c r="AN218" s="2"/>
       <c r="CD218" s="2"/>
     </row>
-    <row r="219" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C219" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B235" s="2"/>
     </row>
-    <row r="249" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B249" s="2"/>
     </row>
-    <row r="255" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="1" t="s">
         <v>0</v>
       </c>
@@ -10411,14 +11334,14 @@
         <v>39</v>
       </c>
     </row>
-    <row r="256" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B256" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AN256" s="2"/>
       <c r="CD256" s="2"/>
     </row>
-    <row r="257" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="257" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B257" s="2"/>
       <c r="C257" s="1" t="s">
         <v>41</v>
@@ -10426,18 +11349,18 @@
       <c r="AN257" s="2"/>
       <c r="CD257" s="2"/>
     </row>
-    <row r="258" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C258" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="266" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="266" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B266" s="2"/>
     </row>
-    <row r="275" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="275" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B275" s="2"/>
     </row>
-    <row r="294" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" s="1" t="s">
         <v>0</v>
       </c>
@@ -10445,14 +11368,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="295" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B295" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AN295" s="2"/>
       <c r="CD295" s="2"/>
     </row>
-    <row r="296" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B296" s="2"/>
       <c r="C296" s="1" t="s">
         <v>48</v>
@@ -10460,7 +11383,7 @@
       <c r="AN296" s="2"/>
       <c r="CD296" s="2"/>
     </row>
-    <row r="297" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B297" s="2"/>
       <c r="C297" s="1" t="s">
         <v>51</v>
@@ -10468,26 +11391,26 @@
       <c r="AN297" s="2"/>
       <c r="CD297" s="2"/>
     </row>
-    <row r="298" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C298" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="299" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C299" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="301" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B301" s="3"/>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B324" s="2"/>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B333" s="2"/>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" s="1" t="s">
         <v>0</v>
       </c>
@@ -10495,14 +11418,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="337" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B337" s="2" t="s">
         <v>53</v>
       </c>
       <c r="AN337" s="2"/>
       <c r="CD337" s="2"/>
     </row>
-    <row r="338" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B338" s="2"/>
       <c r="C338" s="1" t="s">
         <v>54</v>
@@ -10510,7 +11433,7 @@
       <c r="AN338" s="2"/>
       <c r="CD338" s="2"/>
     </row>
-    <row r="351" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" s="1" t="s">
         <v>0</v>
       </c>
@@ -10518,14 +11441,14 @@
         <v>55</v>
       </c>
     </row>
-    <row r="352" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B352" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AN352" s="2"/>
       <c r="CD352" s="2"/>
     </row>
-    <row r="353" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="353" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B353" s="2"/>
       <c r="C353" s="1" t="s">
         <v>57</v>
@@ -10533,13 +11456,13 @@
       <c r="AN353" s="2"/>
       <c r="CD353" s="2"/>
     </row>
-    <row r="376" spans="1:82" s="7" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="376" spans="1:82" s="7" customFormat="1" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B376" s="8"/>
     </row>
-    <row r="377" spans="1:82" s="9" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:82" s="9" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B377" s="10"/>
     </row>
-    <row r="378" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" s="1" t="s">
         <v>0</v>
       </c>
@@ -10547,14 +11470,14 @@
         <v>58</v>
       </c>
     </row>
-    <row r="379" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B379" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AN379" s="2"/>
       <c r="CD379" s="2"/>
     </row>
-    <row r="380" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B380" s="2"/>
       <c r="C380" s="1" t="s">
         <v>44</v>
@@ -10562,18 +11485,18 @@
       <c r="AN380" s="2"/>
       <c r="CD380" s="2"/>
     </row>
-    <row r="381" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C381" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="389" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="389" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B389" s="2"/>
     </row>
-    <row r="401" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="401" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B401" s="2"/>
     </row>
-    <row r="417" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A417" s="1" t="s">
         <v>0</v>
       </c>
@@ -10581,14 +11504,14 @@
         <v>61</v>
       </c>
     </row>
-    <row r="418" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B418" s="2" t="s">
         <v>62</v>
       </c>
       <c r="AN418" s="2"/>
       <c r="CD418" s="2"/>
     </row>
-    <row r="419" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B419" s="2"/>
       <c r="C419" s="1" t="s">
         <v>60</v>
@@ -10596,15 +11519,15 @@
       <c r="AN419" s="2"/>
       <c r="CD419" s="2"/>
     </row>
-    <row r="420" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C420" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="430" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B430" s="2"/>
     </row>
-    <row r="433" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A433" s="1" t="s">
         <v>0</v>
       </c>
@@ -10612,14 +11535,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="434" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B434" s="2" t="s">
         <v>64</v>
       </c>
       <c r="AN434" s="2"/>
       <c r="CD434" s="2"/>
     </row>
-    <row r="435" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B435" s="2"/>
       <c r="C435" s="1" t="s">
         <v>65</v>
@@ -10627,12 +11550,12 @@
       <c r="AN435" s="2"/>
       <c r="CD435" s="2"/>
     </row>
-    <row r="436" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B436" s="3"/>
     </row>
-    <row r="451" spans="1:82" s="4" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="452" spans="1:82" s="5" customFormat="1" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="453" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:82" s="4" customFormat="1" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="452" spans="1:82" s="5" customFormat="1" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="453" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A453" s="1" t="s">
         <v>0</v>
       </c>
@@ -10640,14 +11563,14 @@
         <v>66</v>
       </c>
     </row>
-    <row r="454" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B454" s="2" t="s">
         <v>67</v>
       </c>
       <c r="AN454" s="2"/>
       <c r="CD454" s="2"/>
     </row>
-    <row r="455" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B455" s="2"/>
       <c r="C455" s="1" t="s">
         <v>68</v>
@@ -10655,29 +11578,29 @@
       <c r="AN455" s="2"/>
       <c r="CD455" s="2"/>
     </row>
-    <row r="456" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C456" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="457" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C457" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="462" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B462" s="2"/>
     </row>
-    <row r="471" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="471" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B471" s="2"/>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B489" s="2"/>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B490" s="2"/>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A496" s="1" t="s">
         <v>0</v>
       </c>
@@ -10685,27 +11608,27 @@
         <v>71</v>
       </c>
     </row>
-    <row r="497" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="497" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B497" s="2" t="s">
         <v>72</v>
       </c>
       <c r="AN497" s="2"/>
       <c r="CD497" s="2"/>
     </row>
-    <row r="498" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="498" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B498" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="499" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="499" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B499" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="516" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B516" s="2"/>
     </row>
-    <row r="518" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A518" s="1" t="s">
         <v>0</v>
       </c>
@@ -10713,22 +11636,22 @@
         <v>75</v>
       </c>
     </row>
-    <row r="519" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B519" s="2" t="s">
         <v>76</v>
       </c>
       <c r="AN519" s="2"/>
       <c r="CD519" s="2"/>
     </row>
-    <row r="520" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B520" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="528" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B528" s="2"/>
     </row>
-    <row r="539" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A539" s="1" t="s">
         <v>0</v>
       </c>
@@ -10736,22 +11659,22 @@
         <v>78</v>
       </c>
     </row>
-    <row r="540" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B540" s="2" t="s">
         <v>79</v>
       </c>
       <c r="AN540" s="2"/>
       <c r="CD540" s="2"/>
     </row>
-    <row r="541" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B541" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="545" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="545" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B545" s="2"/>
     </row>
-    <row r="561" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A561" s="1" t="s">
         <v>0</v>
       </c>
@@ -10759,22 +11682,22 @@
         <v>81</v>
       </c>
     </row>
-    <row r="562" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B562" s="2" t="s">
         <v>82</v>
       </c>
       <c r="AN562" s="2"/>
       <c r="CD562" s="2"/>
     </row>
-    <row r="563" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B563" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="581" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B581" s="2"/>
     </row>
-    <row r="585" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A585" s="1" t="s">
         <v>0</v>
       </c>
@@ -10782,24 +11705,24 @@
         <v>84</v>
       </c>
     </row>
-    <row r="586" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B586" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AN586" s="2"/>
       <c r="CD586" s="2"/>
     </row>
-    <row r="587" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B587" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="588" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B588" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="609" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A609" s="1" t="s">
         <v>0</v>
       </c>
@@ -10807,22 +11730,22 @@
         <v>88</v>
       </c>
     </row>
-    <row r="610" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B610" s="2" t="s">
         <v>89</v>
       </c>
       <c r="AN610" s="2"/>
       <c r="CD610" s="2"/>
     </row>
-    <row r="611" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B611" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="627" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B627" s="2"/>
     </row>
-    <row r="628" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A628" s="1" t="s">
         <v>0</v>
       </c>
@@ -10830,34 +11753,34 @@
         <v>91</v>
       </c>
     </row>
-    <row r="629" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B629" s="2" t="s">
         <v>92</v>
       </c>
       <c r="AN629" s="2"/>
       <c r="CD629" s="2"/>
     </row>
-    <row r="630" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B630" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="631" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B631" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="632" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B632" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="633" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B633" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="652" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A652" s="1" t="s">
         <v>0</v>
       </c>
@@ -10865,26 +11788,26 @@
         <v>141</v>
       </c>
     </row>
-    <row r="653" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B653" s="2" t="s">
         <v>142</v>
       </c>
       <c r="AN653" s="2"/>
       <c r="CD653" s="2"/>
     </row>
-    <row r="654" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C654" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="655" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="C655" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="693" spans="1:82" s="11" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="694" spans="1:82" s="12" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="695" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:82" s="11" customFormat="1" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="694" spans="1:82" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="695" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A695" s="1" t="s">
         <v>0</v>
       </c>
@@ -10892,32 +11815,32 @@
         <v>116</v>
       </c>
     </row>
-    <row r="696" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B696" s="2" t="s">
         <v>97</v>
       </c>
       <c r="AN696" s="2"/>
       <c r="CD696" s="2"/>
     </row>
-    <row r="697" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B697" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="698" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B698" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="699" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B699" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="702" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B702" s="2"/>
     </row>
-    <row r="715" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A715" s="1" t="s">
         <v>0</v>
       </c>
@@ -10925,26 +11848,26 @@
         <v>117</v>
       </c>
     </row>
-    <row r="716" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B716" s="2" t="s">
         <v>145</v>
       </c>
       <c r="AN716" s="2"/>
       <c r="CD716" s="2"/>
     </row>
-    <row r="717" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B717" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="718" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B718" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="756" spans="1:82" s="11" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="757" spans="1:82" s="12" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="758" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:82" s="11" customFormat="1" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="757" spans="1:82" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="758" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A758" s="1" t="s">
         <v>0</v>
       </c>
@@ -10952,27 +11875,27 @@
         <v>101</v>
       </c>
     </row>
-    <row r="759" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B759" s="2" t="s">
         <v>102</v>
       </c>
       <c r="AN759" s="2"/>
       <c r="CD759" s="2"/>
     </row>
-    <row r="760" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B760" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="761" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B761" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="783" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="783" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B783" s="2"/>
     </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="800" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A800" s="1" t="s">
         <v>0</v>
       </c>
@@ -10980,24 +11903,24 @@
         <v>105</v>
       </c>
     </row>
-    <row r="801" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="801" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B801" s="2" t="s">
         <v>106</v>
       </c>
       <c r="AN801" s="2"/>
       <c r="CD801" s="2"/>
     </row>
-    <row r="802" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="802" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B802" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="803" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="803" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B803" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="817" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="817" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A817" s="1" t="s">
         <v>0</v>
       </c>
@@ -11005,19 +11928,19 @@
         <v>109</v>
       </c>
     </row>
-    <row r="818" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="818" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B818" s="2" t="s">
         <v>110</v>
       </c>
       <c r="AN818" s="2"/>
       <c r="CD818" s="2"/>
     </row>
-    <row r="819" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="819" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B819" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="858" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="858" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A858" s="1" t="s">
         <v>0</v>
       </c>
@@ -11025,26 +11948,26 @@
         <v>112</v>
       </c>
     </row>
-    <row r="859" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="859" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B859" s="2" t="s">
         <v>113</v>
       </c>
       <c r="AN859" s="2"/>
       <c r="CD859" s="2"/>
     </row>
-    <row r="860" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="860" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B860" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="861" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="861" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B861" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="874" spans="1:82" s="4" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="875" spans="1:82" s="5" customFormat="1" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="876" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="874" spans="1:82" s="4" customFormat="1" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="875" spans="1:82" s="5" customFormat="1" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="876" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A876" s="1" t="s">
         <v>0</v>
       </c>
@@ -11052,19 +11975,19 @@
         <v>120</v>
       </c>
     </row>
-    <row r="877" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="877" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B877" s="2" t="s">
         <v>121</v>
       </c>
       <c r="AN877" s="2"/>
       <c r="CD877" s="2"/>
     </row>
-    <row r="878" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="878" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B878" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="918" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="918" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A918" s="1" t="s">
         <v>0</v>
       </c>
@@ -11072,24 +11995,24 @@
         <v>123</v>
       </c>
     </row>
-    <row r="919" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="919" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B919" s="2" t="s">
         <v>124</v>
       </c>
       <c r="AN919" s="2"/>
       <c r="CD919" s="2"/>
     </row>
-    <row r="920" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="920" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B920" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="921" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="921" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B921" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="954" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="954" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A954" s="1" t="s">
         <v>0</v>
       </c>
@@ -11097,14 +12020,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="955" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="955" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B955" s="2" t="s">
         <v>128</v>
       </c>
       <c r="AN955" s="2"/>
       <c r="CD955" s="2"/>
     </row>
-    <row r="995" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="995" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A995" s="1" t="s">
         <v>0</v>
       </c>
@@ -11112,16 +12035,16 @@
         <v>129</v>
       </c>
     </row>
-    <row r="996" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="996" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B996" s="2" t="s">
         <v>130</v>
       </c>
       <c r="AN996" s="2"/>
       <c r="CD996" s="2"/>
     </row>
-    <row r="1009" spans="1:82" s="4" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="1010" spans="1:82" s="5" customFormat="1" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="1011" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="1009" spans="1:82" s="4" customFormat="1" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="1010" spans="1:82" s="5" customFormat="1" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="1011" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A1011" s="1" t="s">
         <v>0</v>
       </c>
@@ -11129,19 +12052,19 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1012" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="1012" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B1012" s="2" t="s">
         <v>132</v>
       </c>
       <c r="AN1012" s="2"/>
       <c r="CD1012" s="2"/>
     </row>
-    <row r="1013" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="1013" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B1013" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="1051" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="1051" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A1051" s="1" t="s">
         <v>0</v>
       </c>
@@ -11149,34 +12072,34 @@
         <v>134</v>
       </c>
     </row>
-    <row r="1052" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="1052" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B1052" s="2" t="s">
         <v>135</v>
       </c>
       <c r="AN1052" s="2"/>
       <c r="CD1052" s="2"/>
     </row>
-    <row r="1053" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="1053" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B1053" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="1054" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="1054" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B1054" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="1055" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="1055" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B1055" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="1056" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="1056" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B1056" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="1057" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="1057" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B1057" s="1" t="s">
         <v>140</v>
       </c>
@@ -11192,12 +12115,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87211F2-F883-4DD1-BBC1-872CEC5E75B5}">
   <dimension ref="A2:CD612"/>
-  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="16384" width="3.09765625" style="1"/>
+    <col min="1" max="16384" width="3.08203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -11205,17 +12128,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="AN3" s="2"/>
       <c r="CD3" s="2"/>
     </row>
-    <row r="33" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="2"/>
     </row>
-    <row r="38" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -11223,20 +12146,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="2" t="s">
         <v>4</v>
       </c>
       <c r="AN39" s="2"/>
       <c r="CD39" s="2"/>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="2"/>
     </row>
-    <row r="74" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="2"/>
     </row>
-    <row r="77" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="1" t="s">
         <v>0</v>
       </c>
@@ -11244,17 +12167,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AN78" s="2"/>
       <c r="CD78" s="2"/>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="2"/>
     </row>
-    <row r="97" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
@@ -11262,20 +12185,20 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="2" t="s">
         <v>8</v>
       </c>
       <c r="AN98" s="2"/>
       <c r="CD98" s="2"/>
     </row>
-    <row r="104" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="2"/>
     </row>
-    <row r="121" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B121" s="2"/>
     </row>
-    <row r="124" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="1" t="s">
         <v>0</v>
       </c>
@@ -11283,20 +12206,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B125" s="2" t="s">
         <v>10</v>
       </c>
       <c r="AN125" s="2"/>
       <c r="CD125" s="2"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B131" s="2"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B145" s="2"/>
     </row>
-    <row r="163" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="1" t="s">
         <v>0</v>
       </c>
@@ -11304,20 +12227,20 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B164" s="2" t="s">
         <v>12</v>
       </c>
       <c r="AN164" s="2"/>
       <c r="CD164" s="2"/>
     </row>
-    <row r="169" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B169" s="2"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B184" s="2"/>
     </row>
-    <row r="199" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="1" t="s">
         <v>0</v>
       </c>
@@ -11325,23 +12248,23 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B200" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AN200" s="2"/>
       <c r="CD200" s="2"/>
     </row>
-    <row r="203" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B203" s="2"/>
     </row>
-    <row r="207" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B207" s="2"/>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B222" s="2"/>
     </row>
-    <row r="226" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="1" t="s">
         <v>0</v>
       </c>
@@ -11349,74 +12272,74 @@
         <v>15</v>
       </c>
     </row>
-    <row r="227" spans="1:82" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B227" s="2" t="s">
         <v>4</v>
       </c>
       <c r="AN227" s="2"/>
       <c r="CD227" s="2"/>
     </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="242" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B242" s="2"/>
     </row>
-    <row r="261" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="261" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B261" s="2"/>
     </row>
-    <row r="275" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="275" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B275" s="2"/>
     </row>
-    <row r="288" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="288" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B288" s="2"/>
     </row>
-    <row r="297" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="297" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B297" s="2"/>
     </row>
-    <row r="316" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="316" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B316" s="2"/>
     </row>
-    <row r="328" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="328" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B328" s="2"/>
     </row>
-    <row r="340" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="340" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B340" s="2"/>
     </row>
-    <row r="369" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="369" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B369" s="2"/>
     </row>
-    <row r="372" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="372" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B372" s="3"/>
     </row>
-    <row r="395" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="395" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B395" s="2"/>
     </row>
-    <row r="404" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="404" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B404" s="2"/>
     </row>
-    <row r="422" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="422" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B422" s="2"/>
     </row>
-    <row r="423" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="423" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B423" s="2"/>
     </row>
-    <row r="449" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="449" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B449" s="2"/>
     </row>
-    <row r="458" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="458" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B458" s="2"/>
     </row>
-    <row r="475" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="475" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B475" s="2"/>
     </row>
-    <row r="508" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="508" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B508" s="2"/>
     </row>
-    <row r="550" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="550" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B550" s="2"/>
     </row>
-    <row r="577" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="577" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B577" s="2"/>
     </row>
-    <row r="612" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="612" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B612" s="2"/>
     </row>
   </sheetData>
